--- a/data-manipulation-scripts/sheets-cleanup/sheets/ESPACADOR 16_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ESPACADOR 16_02.xlsx
@@ -28,16 +28,16 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>ESPACADOR DIAN ESQUERDA IRON CG160 ESD  196831</t>
+    <t>ESPACADOR DIANTEIRA ESQUERDA IRON CG160 ESD  196831</t>
   </si>
   <si>
-    <t>ESPACADOR TRA ESQUERDA IRON POP100 110I 196535</t>
+    <t>ESPACADOR TRASEIRA ESQUERDA IRON POP100 110I 196535</t>
   </si>
   <si>
     <t>618341653979</t>
   </si>
   <si>
-    <t>ESPACADOR TRA DIREITA IRON POP100 110I 2007 A 2016 196523</t>
+    <t>ESPACADOR TRASEIRA DIREITA IRON POP100 110I 2007 A 2016 196523</t>
   </si>
 </sst>
 </file>
@@ -343,7 +343,9 @@
       <c r="C2" s="2">
         <v>5.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -355,7 +357,9 @@
       <c r="C3" s="2">
         <v>10.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -365,7 +369,9 @@
         <v>8</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
